--- a/rnaseq-with-probes/v5.0.0/rnaseq-with-probes-v5.0.0.xlsx
+++ b/rnaseq-with-probes/v5.0.0/rnaseq-with-probes-v5.0.0.xlsx
@@ -453,7 +453,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="819">
   <si>
     <t>assay_description</t>
   </si>
@@ -566,6 +566,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000479</t>
   </si>
   <si>
+    <t>snm3C-seq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000504</t>
+  </si>
+  <si>
     <t>seqFISH</t>
   </si>
   <si>
@@ -2231,6 +2237,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000359</t>
   </si>
   <si>
+    <t>Illumina; IDT for Illumina - TruSeq RNA UD Indexes (96 Indexes, 96 Samples); PN 20022371</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000505</t>
+  </si>
+  <si>
     <t>10x Genomics; Chromium i7 Multiplex Kit N, Set A, 96 rxn; PN 1000084</t>
   </si>
   <si>
@@ -2891,7 +2903,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2026-08-17T08:18:06-07:00</t>
+    <t>2026-08-26T14:13:11-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -3093,162 +3105,162 @@
         <v>4</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="AQ1" t="s" s="1">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="AR1" t="s" s="1">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="AS1" t="s" s="1">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="AT1" t="s" s="1">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="AU1" t="s" s="1">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="AV1" t="s" s="1">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="AW1" t="s" s="1">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="AX1" t="s" s="1">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="AY1" t="s" s="1">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="AZ1" t="s" s="1">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="BA1" t="s" s="1">
-        <v>806</v>
+        <v>810</v>
       </c>
     </row>
     <row r="2">
       <c r="E2" t="s" s="6">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BA2" t="s" s="54">
-        <v>807</v>
+        <v>811</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="41">
     <dataValidation type="list" sqref="E2:E1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'dataset_type'!$A$1:$A$58</formula1>
+      <formula1>'dataset_type'!$A$1:$A$59</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F2:F1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'analyte_class'!$A$1:$A$18</formula1>
@@ -3348,7 +3360,7 @@
       <formula1>'library_preparation_kit'!$A$1:$A$40</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AL2:AL1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'sample_indexing_kit'!$A$1:$A$19</formula1>
+      <formula1>'sample_indexing_kit'!$A$1:$A$20</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AN2:AN1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'is_technical_replicate'!$A$1:$A$2</formula1>
@@ -3396,26 +3408,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -3430,42 +3442,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3480,22 +3492,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3510,26 +3522,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -3544,32 +3556,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3584,42 +3596,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -3634,18 +3646,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -3660,18 +3672,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -3686,18 +3698,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -3712,26 +3724,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -3741,7 +3753,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4206,6 +4218,14 @@
       </c>
       <c r="B58" t="s" s="0">
         <v>120</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -4220,18 +4240,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -4246,322 +4266,322 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
   </sheetData>
@@ -4571,159 +4591,167 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>607</v>
+        <v>609</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>610</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -4738,12 +4766,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4758,242 +4786,242 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -5008,90 +5036,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -5106,154 +5134,154 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>692</v>
+        <v>696</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
   </sheetData>
@@ -5268,162 +5296,162 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>711</v>
+        <v>715</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>715</v>
+        <v>719</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>717</v>
+        <v>721</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>721</v>
+        <v>725</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>729</v>
+        <v>733</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>735</v>
+        <v>739</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>737</v>
+        <v>741</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>741</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -5438,18 +5466,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -5464,250 +5492,250 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>756</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>758</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>772</v>
+        <v>776</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>774</v>
+        <v>778</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>776</v>
+        <v>780</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>778</v>
+        <v>782</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>780</v>
+        <v>784</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>782</v>
+        <v>786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>784</v>
+        <v>788</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>786</v>
+        <v>790</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>788</v>
+        <v>792</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>790</v>
+        <v>794</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>792</v>
+        <v>796</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>794</v>
+        <v>798</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>796</v>
+        <v>800</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>798</v>
+        <v>802</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>802</v>
+        <v>806</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>804</v>
+        <v>808</v>
       </c>
     </row>
   </sheetData>
@@ -5722,146 +5750,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -5876,12 +5904,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -5902,30 +5930,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>813</v>
+        <v>817</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>814</v>
+        <v>818</v>
       </c>
     </row>
   </sheetData>
@@ -5940,12 +5968,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -5960,266 +5988,266 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -6234,714 +6262,714 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B87" t="s" s="0">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B88" t="s" s="0">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B89" t="s" s="0">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -6956,42 +6984,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -7006,26 +7034,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -7040,57 +7068,57 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/rnaseq-with-probes/v5.0.0/rnaseq-with-probes-v5.0.0.xlsx
+++ b/rnaseq-with-probes/v5.0.0/rnaseq-with-probes-v5.0.0.xlsx
@@ -453,7 +453,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="844">
   <si>
     <t>assay_description</t>
   </si>
@@ -470,94 +470,322 @@
     <t>dataset_type</t>
   </si>
   <si>
+    <t>Cell DIVE</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000159</t>
+  </si>
+  <si>
+    <t>CODEX</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000160</t>
+  </si>
+  <si>
+    <t>Light Sheet</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000168</t>
+  </si>
+  <si>
+    <t>MIBI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000172</t>
+  </si>
+  <si>
+    <t>LC-MS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000194</t>
+  </si>
+  <si>
     <t>HiFi-Slide</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000195</t>
   </si>
   <si>
+    <t>Histology</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000197</t>
+  </si>
+  <si>
+    <t>PhenoCycler</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000199</t>
+  </si>
+  <si>
+    <t>CyCIF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000200</t>
+  </si>
+  <si>
+    <t>MALDI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000201</t>
+  </si>
+  <si>
+    <t>SIMS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000202</t>
+  </si>
+  <si>
+    <t>DESI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000204</t>
+  </si>
+  <si>
+    <t>Auto-fluorescence</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000205</t>
+  </si>
+  <si>
+    <t>Confocal</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000206</t>
+  </si>
+  <si>
+    <t>Thick section Multiphoton MxIF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000207</t>
+  </si>
+  <si>
+    <t>Second Harmonic Generation (SHG)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000208</t>
+  </si>
+  <si>
+    <t>Enhanced Stimulated Raman Spectroscopy (SRS)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000209</t>
+  </si>
+  <si>
+    <t>10X Multiome</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000215</t>
+  </si>
+  <si>
+    <t>Molecular Cartography</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000217</t>
+  </si>
+  <si>
+    <t>CosMx Transcriptomics</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000218</t>
+  </si>
+  <si>
+    <t>Xenium</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000219</t>
+  </si>
+  <si>
+    <t>MERFISH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000221</t>
+  </si>
+  <si>
     <t>SNARE-seq2</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000264</t>
   </si>
   <si>
+    <t>2D Imaging Mass Cytometry</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000296</t>
+  </si>
+  <si>
+    <t>GeoMx (NGS)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000300</t>
+  </si>
+  <si>
+    <t>GeoMx (nCounter)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000301</t>
+  </si>
+  <si>
+    <t>Visium (no probes)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000302</t>
+  </si>
+  <si>
+    <t>Visium (with probes)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000303</t>
+  </si>
+  <si>
+    <t>ATACseq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000309</t>
+  </si>
+  <si>
+    <t>RNAseq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000310</t>
+  </si>
+  <si>
+    <t>RNAseq (with probes)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000311</t>
+  </si>
+  <si>
+    <t>nanoSPLITS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000312</t>
+  </si>
+  <si>
+    <t>MUSIC</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000328</t>
+  </si>
+  <si>
+    <t>Resolve</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000384</t>
+  </si>
+  <si>
+    <t>Stereo-seq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000385</t>
+  </si>
+  <si>
+    <t>Seq-Scope</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000390</t>
+  </si>
+  <si>
+    <t>DART-FISH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000396</t>
+  </si>
+  <si>
+    <t>seqFISH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000397</t>
+  </si>
+  <si>
+    <t>MS Lipidomics</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000405</t>
+  </si>
+  <si>
+    <t>CyTOF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000407</t>
+  </si>
+  <si>
+    <t>DBiT-seq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000428</t>
+  </si>
+  <si>
+    <t>Singular Genomics G4X</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000429</t>
+  </si>
+  <si>
+    <t>CosMx Proteomics</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000435</t>
+  </si>
+  <si>
+    <t>FACS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000440</t>
+  </si>
+  <si>
+    <t>Olink</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000441</t>
+  </si>
+  <si>
+    <t>4i</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000447</t>
+  </si>
+  <si>
+    <t>MPLEx</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000448</t>
+  </si>
+  <si>
+    <t>Pixel-seqV2</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000450</t>
+  </si>
+  <si>
+    <t>Visium HD</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000451</t>
+  </si>
+  <si>
     <t>COMET</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000458</t>
   </si>
   <si>
-    <t>Visium (no probes)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000302</t>
-  </si>
-  <si>
-    <t>DESI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000204</t>
-  </si>
-  <si>
-    <t>Confocal</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000206</t>
-  </si>
-  <si>
-    <t>Stereo-seq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000385</t>
-  </si>
-  <si>
-    <t>Visium (with probes)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000303</t>
-  </si>
-  <si>
-    <t>Molecular Cartography</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000217</t>
-  </si>
-  <si>
     <t>Virtual Histology</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000473</t>
   </si>
   <si>
-    <t>DBiT-seq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000428</t>
-  </si>
-  <si>
-    <t>Seq-Scope</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000390</t>
-  </si>
-  <si>
-    <t>CosMx Transcriptomics</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000218</t>
-  </si>
-  <si>
-    <t>CyCIF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000200</t>
-  </si>
-  <si>
-    <t>Light Sheet</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000168</t>
+    <t>Raman Imaging</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000475</t>
+  </si>
+  <si>
+    <t>STARmap</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000476</t>
   </si>
   <si>
     <t>iCLAP</t>
@@ -566,283 +794,145 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000479</t>
   </si>
   <si>
+    <t>MACSima</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000480</t>
+  </si>
+  <si>
+    <t>Illumina Spatial ver0</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000487</t>
+  </si>
+  <si>
+    <t>DNA Methylation</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000490</t>
+  </si>
+  <si>
+    <t>Paired-Tag</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000492</t>
+  </si>
+  <si>
     <t>snm3C-seq</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000504</t>
   </si>
   <si>
-    <t>seqFISH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000397</t>
-  </si>
-  <si>
-    <t>ATACseq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000309</t>
-  </si>
-  <si>
-    <t>CosMx Proteomics</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000435</t>
-  </si>
-  <si>
-    <t>Singular Genomics G4X</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000429</t>
-  </si>
-  <si>
-    <t>Visium HD</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000451</t>
-  </si>
-  <si>
-    <t>MERFISH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000221</t>
-  </si>
-  <si>
-    <t>10X Multiome</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000215</t>
-  </si>
-  <si>
-    <t>4i</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000447</t>
-  </si>
-  <si>
-    <t>PhenoCycler</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000199</t>
-  </si>
-  <si>
-    <t>Second Harmonic Generation (SHG)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000208</t>
-  </si>
-  <si>
-    <t>Thick section Multiphoton MxIF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000207</t>
-  </si>
-  <si>
-    <t>MACSima</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000480</t>
-  </si>
-  <si>
-    <t>CyTOF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000407</t>
-  </si>
-  <si>
-    <t>Olink</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000441</t>
-  </si>
-  <si>
-    <t>MIBI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000172</t>
-  </si>
-  <si>
-    <t>Auto-fluorescence</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000205</t>
-  </si>
-  <si>
-    <t>FACS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000440</t>
-  </si>
-  <si>
-    <t>Xenium</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000219</t>
-  </si>
-  <si>
-    <t>DNA Methylation</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000490</t>
-  </si>
-  <si>
-    <t>SIMS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000202</t>
-  </si>
-  <si>
-    <t>Cell DIVE</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000159</t>
-  </si>
-  <si>
-    <t>CODEX</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000160</t>
-  </si>
-  <si>
-    <t>GeoMx (NGS)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000300</t>
-  </si>
-  <si>
-    <t>MUSIC</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000328</t>
-  </si>
-  <si>
-    <t>Pixel-seqV2</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000450</t>
-  </si>
-  <si>
-    <t>MALDI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000201</t>
-  </si>
-  <si>
-    <t>2D Imaging Mass Cytometry</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000296</t>
-  </si>
-  <si>
-    <t>Histology</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000197</t>
-  </si>
-  <si>
-    <t>Enhanced Stimulated Raman Spectroscopy (SRS)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000209</t>
-  </si>
-  <si>
-    <t>Illumina Spatial ver0</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000487</t>
-  </si>
-  <si>
-    <t>DART-FISH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000396</t>
-  </si>
-  <si>
-    <t>Resolve</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000384</t>
-  </si>
-  <si>
-    <t>RNAseq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000310</t>
-  </si>
-  <si>
-    <t>LC-MS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000194</t>
-  </si>
-  <si>
-    <t>nanoSPLITS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000312</t>
-  </si>
-  <si>
-    <t>GeoMx (nCounter)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000301</t>
-  </si>
-  <si>
-    <t>Raman Imaging</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000475</t>
-  </si>
-  <si>
-    <t>RNAseq (with probes)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000311</t>
-  </si>
-  <si>
-    <t>Paired-Tag</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000492</t>
-  </si>
-  <si>
-    <t>MS Lipidomics</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000405</t>
-  </si>
-  <si>
-    <t>STARmap</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000476</t>
-  </si>
-  <si>
-    <t>MPLEx</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000448</t>
+    <t>Whole Exome Sequencing</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000514</t>
   </si>
   <si>
     <t>analyte_class</t>
   </si>
   <si>
+    <t>Chromatin</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C13201</t>
+  </si>
+  <si>
+    <t>Collagen</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C16447</t>
+  </si>
+  <si>
+    <t>Protein</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C17021</t>
+  </si>
+  <si>
+    <t>DNA</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C449</t>
+  </si>
+  <si>
+    <t>Metabolite</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C61154</t>
+  </si>
+  <si>
+    <t>Lipid</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C616</t>
+  </si>
+  <si>
+    <t>Peptide</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C735</t>
+  </si>
+  <si>
+    <t>RNA</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C812</t>
+  </si>
+  <si>
+    <t>Polysaccharide</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/CHEBI_18154</t>
+  </si>
+  <si>
+    <t>Fluorochrome</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/CHEBI_51217</t>
+  </si>
+  <si>
+    <t>Endogenous fluorophore</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000131</t>
+  </si>
+  <si>
+    <t>Nucleic acid + protein</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000273</t>
+  </si>
+  <si>
     <t>DNA + RNA</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000327</t>
   </si>
   <si>
-    <t>Nucleic acid + protein</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000273</t>
-  </si>
-  <si>
-    <t>Chromatin</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C13201</t>
+    <t>Saturated lipid</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000388</t>
+  </si>
+  <si>
+    <t>Unsaturated lipid</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000389</t>
+  </si>
+  <si>
+    <t>Lipid + metabolite</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000401</t>
+  </si>
+  <si>
+    <t>RNA + protein</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000474</t>
   </si>
   <si>
     <t>Lipid + metabolite + protein</t>
@@ -851,90 +941,6 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000478</t>
   </si>
   <si>
-    <t>RNA + protein</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000474</t>
-  </si>
-  <si>
-    <t>RNA</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C812</t>
-  </si>
-  <si>
-    <t>Metabolite</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C61154</t>
-  </si>
-  <si>
-    <t>Unsaturated lipid</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000389</t>
-  </si>
-  <si>
-    <t>Lipid + metabolite</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000401</t>
-  </si>
-  <si>
-    <t>Saturated lipid</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000388</t>
-  </si>
-  <si>
-    <t>Lipid</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C616</t>
-  </si>
-  <si>
-    <t>Protein</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C17021</t>
-  </si>
-  <si>
-    <t>Fluorochrome</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/CHEBI_51217</t>
-  </si>
-  <si>
-    <t>Collagen</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C16447</t>
-  </si>
-  <si>
-    <t>DNA</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C449</t>
-  </si>
-  <si>
-    <t>Peptide</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C735</t>
-  </si>
-  <si>
-    <t>Polysaccharide</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/CHEBI_18154</t>
-  </si>
-  <si>
-    <t>Endogenous fluorophore</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000131</t>
-  </si>
-  <si>
     <t>is_targeted</t>
   </si>
   <si>
@@ -947,28 +953,175 @@
     <t>acquisition_instrument_vendor</t>
   </si>
   <si>
+    <t>In-House</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C126386</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_003899</t>
+  </si>
+  <si>
+    <t>Thermo Fisher Scientific</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_008452</t>
+  </si>
+  <si>
+    <t>Leica Microsystems</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_008960</t>
+  </si>
+  <si>
+    <t>Miltenyi Biotec</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_008984</t>
+  </si>
+  <si>
+    <t>Illumina</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_010233</t>
+  </si>
+  <si>
+    <t>Hamamatsu</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_017105</t>
+  </si>
+  <si>
+    <t>Bruker</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_017365</t>
+  </si>
+  <si>
+    <t>Cytiva</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023581</t>
+  </si>
+  <si>
+    <t>Leica Biosystems</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023603</t>
+  </si>
+  <si>
+    <t>Keyence</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023604</t>
+  </si>
+  <si>
+    <t>Ionpath</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023605</t>
+  </si>
+  <si>
+    <t>Standard BioTools (Fluidigm)</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023606</t>
+  </si>
+  <si>
+    <t>Zeiss Microscopy</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023607</t>
+  </si>
+  <si>
+    <t>Andor</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023609</t>
+  </si>
+  <si>
+    <t>Sciex</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023651</t>
+  </si>
+  <si>
+    <t>10x Genomics</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023672</t>
+  </si>
+  <si>
+    <t>Akoya Biosciences</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023774</t>
+  </si>
+  <si>
+    <t>Resolve Biosciences</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023911</t>
+  </si>
+  <si>
+    <t>NanoString</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023912</t>
+  </si>
+  <si>
+    <t>Waters</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024589</t>
+  </si>
+  <si>
+    <t>Evident Scientific (Olympus)</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024782</t>
+  </si>
+  <si>
     <t>BGI Genomics</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_024848</t>
   </si>
   <si>
-    <t>Cytiva</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023581</t>
-  </si>
-  <si>
-    <t>Thermo Fisher Scientific</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_008452</t>
-  </si>
-  <si>
-    <t>Zeiss Microscopy</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023607</t>
+    <t>Motic</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024856</t>
+  </si>
+  <si>
+    <t>Huron Digital Pathology</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024996</t>
+  </si>
+  <si>
+    <t>GE Healthcare</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_025461</t>
+  </si>
+  <si>
+    <t>Vizgen</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026274</t>
+  </si>
+  <si>
+    <t>Element Biosciences</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026453</t>
+  </si>
+  <si>
+    <t>Singular Genomics</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026683</t>
   </si>
   <si>
     <t>Complete Genomics</t>
@@ -983,130 +1136,16 @@
     <t>https://identifiers.org/RRID:SCR_027042</t>
   </si>
   <si>
-    <t>GE Healthcare</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_025461</t>
-  </si>
-  <si>
-    <t>Leica Microsystems</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_008960</t>
-  </si>
-  <si>
-    <t>Akoya Biosciences</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023774</t>
-  </si>
-  <si>
-    <t>NanoString</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023912</t>
-  </si>
-  <si>
-    <t>Element Biosciences</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026453</t>
-  </si>
-  <si>
-    <t>Andor</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023609</t>
-  </si>
-  <si>
-    <t>Huron Digital Pathology</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024996</t>
-  </si>
-  <si>
-    <t>Illumina</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_010233</t>
-  </si>
-  <si>
-    <t>Ionpath</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023605</t>
-  </si>
-  <si>
-    <t>Waters</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024589</t>
-  </si>
-  <si>
-    <t>In-House</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C126386</t>
-  </si>
-  <si>
-    <t>Resolve Biosciences</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023911</t>
-  </si>
-  <si>
-    <t>Singular Genomics</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026683</t>
-  </si>
-  <si>
-    <t>Vizgen</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026274</t>
-  </si>
-  <si>
-    <t>Standard BioTools (Fluidigm)</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023606</t>
-  </si>
-  <si>
-    <t>Sciex</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023651</t>
-  </si>
-  <si>
-    <t>Bruker</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_017365</t>
-  </si>
-  <si>
-    <t>Evident Scientific (Olympus)</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024782</t>
-  </si>
-  <si>
-    <t>Keyence</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023604</t>
-  </si>
-  <si>
-    <t>Miltenyi Biotec</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_008984</t>
-  </si>
-  <si>
-    <t>Leica Biosystems</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023603</t>
+    <t>Cytek Biosciences</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027071</t>
+  </si>
+  <si>
+    <t>Microscopes International</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027094</t>
   </si>
   <si>
     <t>Revvity</t>
@@ -1115,55 +1154,313 @@
     <t>https://identifiers.org/RRID:SCR_027779</t>
   </si>
   <si>
-    <t>Cytek Biosciences</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027071</t>
-  </si>
-  <si>
-    <t>10x Genomics</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023672</t>
-  </si>
-  <si>
-    <t>Microscopes International</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027094</t>
-  </si>
-  <si>
-    <t>Hamamatsu</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_017105</t>
-  </si>
-  <si>
-    <t>Motic</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024856</t>
+    <t>MGI Tech</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_029020</t>
   </si>
   <si>
     <t>acquisition_instrument_model</t>
   </si>
   <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C17998</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C48660</t>
+  </si>
+  <si>
+    <t>NextSeq 500</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_014983</t>
+  </si>
+  <si>
+    <t>NextSeq 550</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_016381</t>
+  </si>
+  <si>
+    <t>HiSeq 2500</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_016383</t>
+  </si>
+  <si>
+    <t>HiSeq 4000</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_016386</t>
+  </si>
+  <si>
+    <t>NovaSeq 6000</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_016387</t>
+  </si>
+  <si>
+    <t>iScan System</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_016388</t>
+  </si>
+  <si>
+    <t>BZ-X710</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_017202</t>
+  </si>
+  <si>
+    <t>LSM 710 Confocal Microscope</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_018063</t>
+  </si>
+  <si>
+    <t>Helios</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_019916</t>
+  </si>
+  <si>
+    <t>QTRAP 5500</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020517</t>
+  </si>
+  <si>
+    <t>Q Exactive HF</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020558</t>
+  </si>
+  <si>
+    <t>Orbitrap Fusion Tribrid</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020559</t>
+  </si>
+  <si>
+    <t>Orbitrap Fusion Lumos Tribrid</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020562</t>
+  </si>
+  <si>
+    <t>Q Exactive HF-X</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020564</t>
+  </si>
+  <si>
+    <t>Q Exactive</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020565</t>
+  </si>
+  <si>
+    <t>Q Exactive UHMR</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020571</t>
+  </si>
+  <si>
+    <t>Zeiss LightSheet Z.1</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020919</t>
+  </si>
+  <si>
+    <t>Axio Scan.Z1</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020927</t>
+  </si>
+  <si>
+    <t>Aperio AT2</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_021256</t>
+  </si>
+  <si>
+    <t>NanoZoomer 2.0-HT</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_021658</t>
+  </si>
+  <si>
+    <t>Digital Spatial Profiler</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_021660</t>
+  </si>
+  <si>
+    <t>Biomark HD</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_022658</t>
+  </si>
+  <si>
+    <t>Hyperion Imaging System</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023195</t>
+  </si>
+  <si>
+    <t>PhenoImager Fusion</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023274</t>
+  </si>
+  <si>
+    <t>Zyla 4.2 sCMOS</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023610</t>
+  </si>
+  <si>
     <t>SCN400</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_023611</t>
   </si>
   <si>
+    <t>MIBIscope</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023613</t>
+  </si>
+  <si>
+    <t>NextSeq 2000</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023614</t>
+  </si>
+  <si>
+    <t>timsTOF FleX MALDI-2</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023615</t>
+  </si>
+  <si>
+    <t>IN Cell Analyzer 2200</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023616</t>
+  </si>
+  <si>
+    <t>BZ-X800</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023617</t>
+  </si>
+  <si>
+    <t>Orbitrap Eclipse Tribrid</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023618</t>
+  </si>
+  <si>
+    <t>Axio Observer 5</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023692</t>
+  </si>
+  <si>
+    <t>Axio Observer 3</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023693</t>
+  </si>
+  <si>
+    <t>Axio Observer 7</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023694</t>
+  </si>
+  <si>
+    <t>NanoZoomer S210</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023760</t>
+  </si>
+  <si>
+    <t>NanoZoomer S360</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023761</t>
+  </si>
+  <si>
+    <t>NanoZoomer S60</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023762</t>
+  </si>
+  <si>
+    <t>NanoZoomer-SQ</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023763</t>
+  </si>
+  <si>
+    <t>Phenocycler-Fusion 2.0</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023773</t>
+  </si>
+  <si>
+    <t>CosMx Spatial Molecular Imager</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023909</t>
+  </si>
+  <si>
+    <t>Xenium Analyzer</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023910</t>
+  </si>
+  <si>
+    <t>Lightsheet 7</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024448</t>
+  </si>
+  <si>
+    <t>Resolve Biosciences Molecular Cartography</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024449</t>
+  </si>
+  <si>
+    <t>NovaSeq X Plus</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024568</t>
+  </si>
+  <si>
+    <t>NovaSeq X</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024569</t>
+  </si>
+  <si>
     <t>STELLARIS 5</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_024663</t>
   </si>
   <si>
-    <t>BZ-X710</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_017202</t>
+    <t>VS200 Slide Scanner</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024783</t>
   </si>
   <si>
     <t>Pannoramic MIDI II Digital Scanner</t>
@@ -1172,10 +1469,10 @@
     <t>https://identifiers.org/RRID:SCR_024834</t>
   </si>
   <si>
-    <t>Not applicable</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C48660</t>
+    <t>DNBSEQ-T7</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024847</t>
   </si>
   <si>
     <t>MoticEasyScan One</t>
@@ -1184,46 +1481,199 @@
     <t>https://identifiers.org/RRID:SCR_024855</t>
   </si>
   <si>
+    <t>DM6 B</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024857</t>
+  </si>
+  <si>
+    <t>TissueScope LE Slide Scanner</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024995</t>
+  </si>
+  <si>
     <t>EVOS M7000</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_025070</t>
   </si>
   <si>
+    <t>Aperio CS2</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_025111</t>
+  </si>
+  <si>
+    <t>BZ-X810</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_025160</t>
+  </si>
+  <si>
+    <t>MERSCOPE Ultra</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026273</t>
+  </si>
+  <si>
+    <t>CyTOF XT</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026344</t>
+  </si>
+  <si>
+    <t>AVITI24</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026452</t>
+  </si>
+  <si>
+    <t>SYNAPT XS</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026524</t>
+  </si>
+  <si>
+    <t>timsTOF Ultra</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026540</t>
+  </si>
+  <si>
+    <t>timsTOF Ultra 2</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026541</t>
+  </si>
+  <si>
+    <t>timsTOF SCP</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026542</t>
+  </si>
+  <si>
+    <t>timsTOF HT</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026543</t>
+  </si>
+  <si>
+    <t>timsTOF Pro</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026544</t>
+  </si>
+  <si>
+    <t>timsTOF Pro 2</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026545</t>
+  </si>
+  <si>
+    <t>CyTOF 2</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026551</t>
+  </si>
+  <si>
+    <t>DMi8</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026672</t>
+  </si>
+  <si>
+    <t>G4X Spatial Sequencer</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026684</t>
+  </si>
+  <si>
+    <t>timsTOF FleX</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026925</t>
+  </si>
+  <si>
+    <t>Cytek Northern Lights</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027072</t>
+  </si>
+  <si>
+    <t>Axio Zoom.V16</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027090</t>
+  </si>
+  <si>
+    <t>solariX</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027095</t>
+  </si>
+  <si>
+    <t>uScopeHXII-20</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027101</t>
+  </si>
+  <si>
+    <t>Juno System</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027198</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027323</t>
+  </si>
+  <si>
+    <t>Panoramic 150 Digital Scanner</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027467</t>
+  </si>
+  <si>
+    <t>Opera Phenix Plus HCS</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027780</t>
+  </si>
+  <si>
+    <t>SYNAPT G2-Si</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027782</t>
+  </si>
+  <si>
+    <t>Opera Phenix HCS</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027817</t>
+  </si>
+  <si>
+    <t>MACSima System</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027923</t>
+  </si>
+  <si>
+    <t>NanoZoomer 2.0-RS</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_028001</t>
+  </si>
+  <si>
     <t>Orbitrap Astral</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_028684</t>
   </si>
   <si>
-    <t>NovaSeq X</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024569</t>
-  </si>
-  <si>
-    <t>LSM 710 Confocal Microscope</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_018063</t>
-  </si>
-  <si>
-    <t>NanoZoomer 2.0-HT</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_021658</t>
-  </si>
-  <si>
-    <t>timsTOF Ultra 2</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026541</t>
-  </si>
-  <si>
-    <t>Lightsheet 7</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024448</t>
+    <t>Olink Signature Q100</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_028906</t>
   </si>
   <si>
     <t>Phenocycler-Fusion 1.0</t>
@@ -1232,280 +1682,16 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000316</t>
   </si>
   <si>
-    <t>DNBSEQ-T7</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024847</t>
-  </si>
-  <si>
-    <t>timsTOF Pro</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026544</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C17998</t>
-  </si>
-  <si>
-    <t>AVITI</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026452</t>
-  </si>
-  <si>
-    <t>DMi8</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026672</t>
-  </si>
-  <si>
-    <t>Opera Phenix Plus HCS</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027780</t>
-  </si>
-  <si>
-    <t>timsTOF Pro 2</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026545</t>
-  </si>
-  <si>
-    <t>Q Exactive UHMR</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_020571</t>
-  </si>
-  <si>
-    <t>Q Exactive</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_020565</t>
-  </si>
-  <si>
-    <t>timsTOF SCP</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026542</t>
-  </si>
-  <si>
-    <t>Zyla 4.2 sCMOS</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023610</t>
-  </si>
-  <si>
-    <t>Helios</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_019916</t>
-  </si>
-  <si>
-    <t>uScopeHXII-20</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027101</t>
-  </si>
-  <si>
-    <t>Orbitrap Fusion Tribrid</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_020559</t>
-  </si>
-  <si>
     <t>Custom: Multiphoton</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000317</t>
   </si>
   <si>
-    <t>QTRAP 5500</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_020517</t>
-  </si>
-  <si>
-    <t>timsTOF Ultra</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026540</t>
-  </si>
-  <si>
-    <t>BZ-X800</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023617</t>
-  </si>
-  <si>
-    <t>CyTOF 2</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026551</t>
-  </si>
-  <si>
-    <t>G4X Spatial Sequencer</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026684</t>
-  </si>
-  <si>
-    <t>NextSeq 500</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_014983</t>
-  </si>
-  <si>
-    <t>NanoZoomer S360</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023761</t>
-  </si>
-  <si>
-    <t>Hyperion Imaging System</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023195</t>
-  </si>
-  <si>
-    <t>NovaSeq X Plus</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024568</t>
-  </si>
-  <si>
-    <t>CyTOF XT</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026344</t>
-  </si>
-  <si>
-    <t>NanoZoomer-SQ</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023763</t>
-  </si>
-  <si>
-    <t>NextSeq 550</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_016381</t>
-  </si>
-  <si>
-    <t>Axio Zoom.V16</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027090</t>
-  </si>
-  <si>
-    <t>Digital Spatial Profiler</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_021660</t>
-  </si>
-  <si>
-    <t>timsTOF FleX</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026925</t>
-  </si>
-  <si>
-    <t>timsTOF FleX MALDI-2</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023615</t>
-  </si>
-  <si>
-    <t>NanoZoomer S210</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023760</t>
-  </si>
-  <si>
-    <t>BZ-X810</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_025160</t>
-  </si>
-  <si>
-    <t>Axio Observer 7</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023694</t>
-  </si>
-  <si>
-    <t>Cytek Northern Lights</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027072</t>
-  </si>
-  <si>
-    <t>iScan System</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_016388</t>
-  </si>
-  <si>
-    <t>Opera Phenix HCS</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027817</t>
-  </si>
-  <si>
-    <t>Zeiss LightSheet Z.1</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_020919</t>
-  </si>
-  <si>
-    <t>IN Cell Analyzer 2200</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023616</t>
-  </si>
-  <si>
-    <t>timsTOF HT</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026543</t>
-  </si>
-  <si>
-    <t>PhenoImager Fusion</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023274</t>
-  </si>
-  <si>
-    <t>DM6 B</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024857</t>
-  </si>
-  <si>
-    <t>Phenocycler-Fusion 2.0</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023773</t>
-  </si>
-  <si>
-    <t>Aperio CS2</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_025111</t>
-  </si>
-  <si>
-    <t>Orbitrap Fusion Lumos Tribrid</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_020562</t>
-  </si>
-  <si>
-    <t>Resolve Biosciences Molecular Cartography</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024449</t>
+    <t>MERSCOPE</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000404</t>
   </si>
   <si>
     <t>MALDI timsTOF Flex Prototype</t>
@@ -1514,177 +1700,30 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000433</t>
   </si>
   <si>
-    <t>TissueScope LE Slide Scanner</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024995</t>
-  </si>
-  <si>
-    <t>VS200 Slide Scanner</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024783</t>
-  </si>
-  <si>
-    <t>Axio Observer 5</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023692</t>
-  </si>
-  <si>
-    <t>NanoZoomer 2.0-RS</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_028001</t>
-  </si>
-  <si>
-    <t>Axio Observer 3</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023693</t>
-  </si>
-  <si>
-    <t>HiSeq 2500</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_016383</t>
-  </si>
-  <si>
-    <t>Orbitrap Eclipse Tribrid</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023618</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027323</t>
-  </si>
-  <si>
-    <t>MERSCOPE</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000404</t>
-  </si>
-  <si>
-    <t>NextSeq 2000</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023614</t>
-  </si>
-  <si>
-    <t>NovaSeq 6000</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_016387</t>
-  </si>
-  <si>
-    <t>HiSeq 4000</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_016386</t>
-  </si>
-  <si>
-    <t>Q Exactive HF-X</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_020564</t>
-  </si>
-  <si>
-    <t>solariX</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027095</t>
-  </si>
-  <si>
-    <t>Panoramic 150 Digital Scanner</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027467</t>
-  </si>
-  <si>
-    <t>Aperio AT2</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_021256</t>
-  </si>
-  <si>
-    <t>MIBIscope</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023613</t>
-  </si>
-  <si>
-    <t>SYNAPT G2-Si</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027782</t>
-  </si>
-  <si>
-    <t>MACSima System</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027923</t>
-  </si>
-  <si>
-    <t>Biomark HD</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_022658</t>
-  </si>
-  <si>
-    <t>NanoZoomer S60</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023762</t>
-  </si>
-  <si>
-    <t>CosMx Spatial Molecular Imager</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023909</t>
-  </si>
-  <si>
-    <t>MERSCOPE Ultra</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_026273</t>
-  </si>
-  <si>
-    <t>Axio Scan.Z1</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_020927</t>
-  </si>
-  <si>
-    <t>Juno System</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_027198</t>
-  </si>
-  <si>
-    <t>Q Exactive HF</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_020558</t>
-  </si>
-  <si>
-    <t>Xenium Analyzer</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023910</t>
-  </si>
-  <si>
     <t>source_storage_duration_value</t>
   </si>
   <si>
     <t>source_storage_duration_unit</t>
   </si>
   <si>
+    <t>minute</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/UO_0000031</t>
+  </si>
+  <si>
     <t>hour</t>
   </si>
   <si>
     <t>http://purl.obolibrary.org/obo/UO_0000032</t>
   </si>
   <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/UO_0000033</t>
+  </si>
+  <si>
     <t>month</t>
   </si>
   <si>
@@ -1697,18 +1736,6 @@
     <t>http://purl.obolibrary.org/obo/UO_0000036</t>
   </si>
   <si>
-    <t>day</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/UO_0000033</t>
-  </si>
-  <si>
-    <t>minute</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/UO_0000031</t>
-  </si>
-  <si>
     <t>time_since_acquisition_instrument_calibration_value</t>
   </si>
   <si>
@@ -1817,16 +1844,22 @@
     <t>assay_input_entity</t>
   </si>
   <si>
+    <t>tissue (bulk)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000267</t>
+  </si>
+  <si>
     <t>single cell</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000268</t>
   </si>
   <si>
-    <t>tissue (bulk)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000267</t>
+    <t>single nucleus</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000269</t>
   </si>
   <si>
     <t>spot</t>
@@ -1835,12 +1868,6 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000270</t>
   </si>
   <si>
-    <t>single nucleus</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000269</t>
-  </si>
-  <si>
     <t>area of interest</t>
   </si>
   <si>
@@ -1898,6 +1925,12 @@
     <t>library_concentration_unit</t>
   </si>
   <si>
+    <t>nM</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/UO_0000065</t>
+  </si>
+  <si>
     <t>ng/ul</t>
   </si>
   <si>
@@ -1910,27 +1943,21 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000438</t>
   </si>
   <si>
-    <t>nM</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/UO_0000065</t>
-  </si>
-  <si>
     <t>library_layout</t>
   </si>
   <si>
+    <t>paired-end</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0000722</t>
+  </si>
+  <si>
     <t>single-end</t>
   </si>
   <si>
     <t>http://purl.obolibrary.org/obo/OBI_0002481</t>
   </si>
   <si>
-    <t>paired-end</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/OBI_0000722</t>
-  </si>
-  <si>
     <t>number_of_iterations_of_cdna_amplification</t>
   </si>
   <si>
@@ -1940,214 +1967,244 @@
     <t>library_preparation_kit</t>
   </si>
   <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C65167</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000250</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 4 rxn; PN 1000285</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000251</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Single Cell 3' GEM, Library &amp; Gel Bead Kit v3, 4 rxns; PN 1000092</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000260</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 4 slides, 16 reactions; PN 1000184</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000261</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 1 slides, 4 reactions; PN 1000187</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000265</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Single Cell 3' Library &amp; Gel Bead Kit, 4 rxns; PN 120267</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000299</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Human Transcriptome, 1 slides, 4 reactions; PN 1000338</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000320</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 6.5mm, 4 reactions; PN 1000520</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000321</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 11 mm, 2 reactions; PN 1000522</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000322</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell 3' GEM, Library &amp; Gel Bead Kit v3.1, 16 rxns; PN 1000121</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000334</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell 3' HT Kit v3.1, 48 rxns; PN 1000348</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000335</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Single Cell 3' HT Kit v3.1, 8 rxns; PN 1000370</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000336</t>
   </si>
   <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 16 rxns; PN 1000268</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000337</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 4 rxns; PN 1000269</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000338</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 16 rxns; PN 1000263</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000339</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 4 rxns; PN 1000265</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000340</t>
+  </si>
+  <si>
+    <t>Parse Biosciences; Evercode WT v2 Kit, 48 rxns; PN ECW02030</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000341</t>
+  </si>
+  <si>
+    <t>Parse Biosciences; Evercode WT Mini v2 Kit, 12 rxns; PN ECW02010</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000342</t>
+  </si>
+  <si>
+    <t>Illumina; TruSeq Stranded mRNA Library Prep (48 samples); PN 20020594</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000343</t>
+  </si>
+  <si>
+    <t>Illumina; TruSeq Stranded mRNA Library Prep (96 samples); PN 20020595</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000344</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Mouse Transcriptome, 4 rxns; PN 1000339</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000355</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Automated Single Cell 5' Kit v2, 24 rxns; PN 1000290</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000365</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Automated Single Cell 5' Kit v2, 4 rxns; PN 1000298</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000366</t>
   </si>
   <si>
+    <t>10X Genomics; Automated Library Construction Kit, 24 rxns; PN 1000428</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000374</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Hybridization &amp; Library Kit, 4 rxns; PN 1000415</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000375</t>
+  </si>
+  <si>
+    <t>New England BioLabs; NEBNext Ultra II RNA Library Prep Kit for Illumina; PN E7770</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000377</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium GEM-X Single Cell 5' Kit v3, 16 rxns; PN 1000699</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000394</t>
+  </si>
+  <si>
+    <t>10x Genomics; Library Construction Kit C, 4 rxns; PN 1000689</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000398</t>
+  </si>
+  <si>
+    <t>10x Genomics; Library Construction Kit C, 16 rxns; PN 1000694</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000399</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium GEM-X Single Cell 3' Kit v4, 16 rxns; PN 1000691</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000400</t>
+  </si>
+  <si>
+    <t>10x Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Mouse Transcriptome, 6.5mm, 4 rxns; PN 1000521</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000432</t>
+  </si>
+  <si>
+    <t>10x Genomics; Library Construction Kit, 16 rxns; PN 1000190</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000439</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Single Cell 3ʹ GEM, Library &amp; Gel Bead Kit v3, 16 rxns; PN 1000075</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000460</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 8 rxns; PN 1000374</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000466</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 48 rxns; PN 1000356</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000467</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000110</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000469</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Next GEM Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000175</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000471</t>
+  </si>
+  <si>
     <t>10x Genomics; Chromium Next GEM Single Cell Fixed RNA Sample Preparation Kit, 16 rxns; PN 1000414</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000484</t>
   </si>
   <si>
-    <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 4 slides, 16 reactions; PN 1000184</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000261</t>
-  </si>
-  <si>
-    <t>Parse Biosciences; Evercode WT v2 Kit, 48 rxns; PN ECW02030</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000341</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 16 rxns; PN 1000263</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000339</t>
-  </si>
-  <si>
-    <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Human Transcriptome, 1 slides, 4 reactions; PN 1000338</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000320</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 16 rxns; PN 1000268</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000337</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Next GEM Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000175</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000471</t>
-  </si>
-  <si>
-    <t>10x Genomics; Library Construction Kit C, 16 rxns; PN 1000694</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000399</t>
-  </si>
-  <si>
-    <t>10x Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Mouse Transcriptome, 6.5mm, 4 rxns; PN 1000521</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000432</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell 3' HT Kit v3.1, 48 rxns; PN 1000348</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000335</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell 3' GEM, Library &amp; Gel Bead Kit v3.1, 16 rxns; PN 1000121</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000334</t>
-  </si>
-  <si>
-    <t>10x Genomics; Library Construction Kit C, 4 rxns; PN 1000689</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000398</t>
-  </si>
-  <si>
-    <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 11 mm, 2 reactions; PN 1000522</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000322</t>
-  </si>
-  <si>
-    <t>Illumina; TruSeq Stranded mRNA Library Prep (48 samples); PN 20020594</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000343</t>
-  </si>
-  <si>
-    <t>10X Genomics; Automated Library Construction Kit, 24 rxns; PN 1000428</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000374</t>
-  </si>
-  <si>
-    <t>New England BioLabs; NEBNext Ultra II RNA Library Prep Kit for Illumina; PN E7770</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000377</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Automated Single Cell 5' Kit v2, 24 rxns; PN 1000290</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000365</t>
-  </si>
-  <si>
-    <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 1 slides, 4 reactions; PN 1000187</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000265</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium GEM-X Single Cell 5' Kit v3, 16 rxns; PN 1000699</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000394</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000110</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000469</t>
-  </si>
-  <si>
-    <t>10x Genomics; Library Construction Kit, 16 rxns; PN 1000190</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000439</t>
-  </si>
-  <si>
-    <t>Parse Biosciences; Evercode WT Mini v2 Kit, 12 rxns; PN ECW02010</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000342</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 48 rxns; PN 1000356</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000467</t>
-  </si>
-  <si>
-    <t>Illumina; TruSeq Stranded mRNA Library Prep (96 samples); PN 20020595</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000344</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 4 rxns; PN 1000265</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000340</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 4 rxn; PN 1000285</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000251</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Hybridization &amp; Library Kit, 4 rxns; PN 1000415</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000375</t>
-  </si>
-  <si>
-    <t>Custom</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C65167</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Single Cell 3' GEM, Library &amp; Gel Bead Kit v3, 4 rxns; PN 1000092</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000260</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Single Cell 3ʹ GEM, Library &amp; Gel Bead Kit v3, 16 rxns; PN 1000075</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000460</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Single Cell 3' Library &amp; Gel Bead Kit, 4 rxns; PN 120267</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000299</t>
-  </si>
-  <si>
-    <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Mouse Transcriptome, 4 rxns; PN 1000339</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000355</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000250</t>
+    <t>10x Genomics; GEM-X Flex GEM &amp; Library Kit, 4 rxns; PN 1000782</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000497</t>
   </si>
   <si>
     <t>Epigenome Technologies; Multiplex Droplet Paired-Tag 16 Reaction Kit; PN MDP16101</t>
@@ -2156,85 +2213,115 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000499</t>
   </si>
   <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 4 rxns; PN 1000269</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000338</t>
-  </si>
-  <si>
-    <t>10x Genomics; GEM-X Flex GEM &amp; Library Kit, 4 rxns; PN 1000782</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000497</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 8 rxns; PN 1000374</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000466</t>
-  </si>
-  <si>
-    <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 6.5mm, 4 reactions; PN 1000520</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000321</t>
+    <t>Takara Bio; SMART-Seq Total RNA Library Prep with ZapR Depletion (with UMIs), 96 rxns; PN 634355</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000507</t>
   </si>
   <si>
     <t>sample_indexing_kit</t>
   </si>
   <si>
+    <t>10X Genomics; Single Index Kit N, Set A (96 rxn); PN 1000212</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000252</t>
+  </si>
+  <si>
+    <t>10X Genomics; Dual Index Kit TT, Set A (96 rxn); PN 1000215</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000253</t>
+  </si>
+  <si>
+    <t>10X Genomics; Dual Index Kit TS, Set A; PN 1000251</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000282</t>
+  </si>
+  <si>
+    <t>Parse Biosciences; Fragmentation Reagents; PN WX100</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000345</t>
+  </si>
+  <si>
+    <t>Parse Biosciences; UDI Plate - WT; PN UDI1001</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000346</t>
+  </si>
+  <si>
+    <t>Illumina; TruSeq RNA Single Indexes Set A (12 Indexes, 48 Samples); PN 20020492</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000347</t>
+  </si>
+  <si>
+    <t>Illumina; TruSeq RNA Single Indexes Set B (12 Indexes, 48 Samples); PN 20020493</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000348</t>
+  </si>
+  <si>
+    <t>Illumina; TruSeq RNA CD Index Plate (96 Indexes, 96 Samples); PN 20019792</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000349</t>
+  </si>
+  <si>
+    <t>Illumina; IDT for Illumina - TruSeq RNA UD Indexes v2 (96 Indexes, 96 Samples); PN 20040871</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000350</t>
+  </si>
+  <si>
+    <t>Integrated DNA Technologies: Custom DNA Oligos</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000351</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; GeoMx Seq Code Pack; PN GMX-NGS-SEQ-AB</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000356</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; GeoMx Seq Code Pack; PN GMX-NGS-SEQ-CD</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000357</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; GeoMx Seq Code Pack; PN GMX-NGS-SEQ-EF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000358</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; GeoMx Seq Code Pack; PN GMX-NGS-SEQ-GH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000359</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium i7 Sample Index Plate (96 rxn); PN 220103</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000380</t>
+  </si>
+  <si>
     <t>10x Genomics; Chromium i7 Multiplex Kit, 96 rxns; PN 120262</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000461</t>
   </si>
   <si>
-    <t>Illumina; TruSeq RNA CD Index Plate (96 Indexes, 96 Samples); PN 20019792</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000349</t>
-  </si>
-  <si>
-    <t>Illumina; TruSeq RNA Single Indexes Set A (12 Indexes, 48 Samples); PN 20020492</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000347</t>
-  </si>
-  <si>
-    <t>Illumina; TruSeq RNA Single Indexes Set B (12 Indexes, 48 Samples); PN 20020493</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000348</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium i7 Sample Index Plate (96 rxn); PN 220103</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000380</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; GeoMx Seq Code Pack; PN GMX-NGS-SEQ-AB</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000356</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; GeoMx Seq Code Pack; PN GMX-NGS-SEQ-CD</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000357</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; GeoMx Seq Code Pack; PN GMX-NGS-SEQ-EF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000358</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; GeoMx Seq Code Pack; PN GMX-NGS-SEQ-GH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000359</t>
+    <t>10x Genomics; Chromium i7 Multiplex Kit N, Set A, 96 rxn; PN 1000084</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000468</t>
   </si>
   <si>
     <t>Illumina; IDT for Illumina - TruSeq RNA UD Indexes (96 Indexes, 96 Samples); PN 20022371</t>
@@ -2243,52 +2330,34 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000505</t>
   </si>
   <si>
-    <t>10x Genomics; Chromium i7 Multiplex Kit N, Set A, 96 rxn; PN 1000084</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000468</t>
-  </si>
-  <si>
-    <t>Parse Biosciences; Fragmentation Reagents; PN WX100</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000345</t>
-  </si>
-  <si>
-    <t>Integrated DNA Technologies: Custom DNA Oligos</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000351</t>
-  </si>
-  <si>
-    <t>Parse Biosciences; UDI Plate - WT; PN UDI1001</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000346</t>
-  </si>
-  <si>
-    <t>10X Genomics; Dual Index Kit TS, Set A; PN 1000251</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000282</t>
-  </si>
-  <si>
-    <t>Illumina; IDT for Illumina - TruSeq RNA UD Indexes v2 (96 Indexes, 96 Samples); PN 20040871</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000350</t>
-  </si>
-  <si>
-    <t>10X Genomics; Single Index Kit N, Set A (96 rxn); PN 1000212</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000252</t>
-  </si>
-  <si>
-    <t>10X Genomics; Dual Index Kit TT, Set A (96 rxn); PN 1000215</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000253</t>
+    <t>Takara Bio; Unique Dual Index Kit (1–96), 96 rxns; PN 634752</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000508</t>
+  </si>
+  <si>
+    <t>Takara Bio; Unique Dual Index Kit (97–192), 96 rxns; PN 634753</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000509</t>
+  </si>
+  <si>
+    <t>Takara Bio; Unique Dual Index Kit (193–288), 96 rxns; PN 634754</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000510</t>
+  </si>
+  <si>
+    <t>Takara Bio; Unique Dual Index Kit (289–384), 96 rxns; PN 634755</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000511</t>
+  </si>
+  <si>
+    <t>Takara Bio; Unique Dual Index Kit (1–24), 24 rxns; PN 634756</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000512</t>
   </si>
   <si>
     <t>sample_indexing_set</t>
@@ -2303,178 +2372,184 @@
     <t>sequencing_reagent_kit</t>
   </si>
   <si>
+    <t>Illumina; HiSeq 3000/4000 PE Cluster Kit PE-410-1001; PN 1000283</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000254</t>
+  </si>
+  <si>
+    <t>Illumina; NextSeq 500/550 Hi Output Kit 150 Cycles; v2.5; PN 20024907</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000255</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq 6000 SP Reagent v1.5 Kit (100 Cycles); PN 20028401</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000256</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq 6000 S1 Reagent v1.5 Kit (100 Cycles); PN 20028319</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000257</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq 6000 S2 Reagent v1.5 Kit (100 Cycles); PN 20028316</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000258</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq 6000 S4 Reagent v1.5 Kit (200 Cycles); PN 20028313</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000259</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq X Series 10B Reagent Kit (300 Cycle); PN 20085594</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000283</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq X Series 10B Reagent Kit (200 Cycle); PN 20085595</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000284</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq X Series 10B Reagent Kit (100 Cycle); PN 20085596</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000285</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq X Series 1.5B Reagent Kit (100 Cycle); PN 20104703</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000286</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq X Series 1.5B Reagent Kit (200 Cycle); PN 20104704</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000287</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq X Series 1.5B Reagent Kit (300 Cycle); PN 20104705</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000288</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq 6000 S1 Reagent Kit (200 Cycles); PN 20012864</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000313</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq 6000 S1 Reagent v1.5 Kit (300 Cycles); PN 20028317</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000318</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq 6000 S4 Reagent Kit v1.5 (300 cycles); PN 20028312</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000319</t>
+  </si>
+  <si>
+    <t>Illumina; NextSeq 1000/2000 P2 Reagent v3 Kit (100 Cycles); PN 20046811</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000323</t>
+  </si>
+  <si>
+    <t>Illumina; NextSeq 1000/2000 P2 Reagent v3 Kit (200 Cycles); PN 20046812</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000352</t>
+  </si>
+  <si>
+    <t>Illumina; NextSeq 1000/2000 P2 Reagent v3 Kit (300 Cycles); PN 20046813</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000353</t>
+  </si>
+  <si>
+    <t>Illumina; NextSeq 2000 P3 Reagent Kit (300 Cycles); PN 20040561</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000354</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq 6000 S1 Reagent v1.5 Kit (200 Cycles); PN 20028318</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000360</t>
+  </si>
+  <si>
+    <t>Illumina; NextSeq 2000 P3 Reagents Kit (100 Cycles); PN 20040559</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000361</t>
+  </si>
+  <si>
+    <t>Illumina; NextSeq 500/550 Mid Output Kit 150 Cycles v2.5; PN 20024904</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000369</t>
+  </si>
+  <si>
+    <t>Illumina; NextSeq 500/550 Hi Output Kit 75 Cycles v2.5; PN 20024906</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000381</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq X Series 25B Reagent Kit (300 Cycle); PN 20104706</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000392</t>
+  </si>
+  <si>
+    <t>Element Biosciences; AVITI 2x75 Sequencing Kit Cloudbreak FS High Output (184 Cycles); PN 860-00015</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000406</t>
+  </si>
+  <si>
+    <t>Illumina; NovaSeq 6000 SP Reagent v1.5 Kit (300 Cycles); PN 20028400</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000459</t>
+  </si>
+  <si>
     <t>Illumina; NovaSeq X Series 25B Reagent Kit (100 Cycle); PN 20125967</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000463</t>
   </si>
   <si>
+    <t>Illumina; NovaSeq X Series 25B Reagent Kit (200 Cycle); PN 20125968</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000464</t>
+  </si>
+  <si>
     <t>Illumina; NextSeq 1000/2000 P2 XLEAP-SBS Reagent Kit (100 Cycles); PN 20100987</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000503</t>
   </si>
   <si>
-    <t>Illumina; NovaSeq X Series 1.5B Reagent Kit (300 Cycle); PN 20104705</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000288</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq 6000 S1 Reagent v1.5 Kit (200 Cycles); PN 20028318</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000360</t>
-  </si>
-  <si>
-    <t>Illumina; NextSeq 2000 P3 Reagent Kit (300 Cycles); PN 20040561</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000354</t>
-  </si>
-  <si>
-    <t>Illumina; NextSeq 1000/2000 P2 Reagent v3 Kit (200 Cycles); PN 20046812</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000352</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq X Series 25B Reagent Kit (200 Cycle); PN 20125968</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000464</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq X Series 1.5B Reagent Kit (200 Cycle); PN 20104704</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000287</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq X Series 10B Reagent Kit (300 Cycle); PN 20085594</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000283</t>
-  </si>
-  <si>
-    <t>Element Biosciences; AVITI 2x75 Sequencing Kit Cloudbreak FS High Output (184 Cycles); PN 860-00015</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000406</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq X Series 1.5B Reagent Kit (100 Cycle); PN 20104703</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000286</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq X Series 25B Reagent Kit (300 Cycle); PN 20104706</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000392</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq 6000 S1 Reagent v1.5 Kit (100 Cycles); PN 20028319</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000257</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq 6000 SP Reagent v1.5 Kit (100 Cycles); PN 20028401</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000256</t>
-  </si>
-  <si>
-    <t>Illumina; HiSeq 3000/4000 PE Cluster Kit PE-410-1001; PN 1000283</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000254</t>
-  </si>
-  <si>
-    <t>Illumina; NextSeq 1000/2000 P2 Reagent v3 Kit (300 Cycles); PN 20046813</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000353</t>
-  </si>
-  <si>
-    <t>Illumina; NextSeq 2000 P3 Reagents Kit (100 Cycles); PN 20040559</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000361</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq 6000 S1 Reagent v1.5 Kit (300 Cycles); PN 20028317</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000318</t>
-  </si>
-  <si>
-    <t>Illumina; NextSeq 1000/2000 P2 Reagent v3 Kit (100 Cycles); PN 20046811</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000323</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq X Series 10B Reagent Kit (200 Cycle); PN 20085595</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000284</t>
-  </si>
-  <si>
-    <t>Illumina; NextSeq 500/550 Hi Output Kit 150 Cycles; v2.5; PN 20024907</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000255</t>
-  </si>
-  <si>
-    <t>Illumina; NextSeq 500/550 Mid Output Kit 150 Cycles v2.5; PN 20024904</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000369</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq 6000 S1 Reagent Kit (200 Cycles); PN 20012864</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000313</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq 6000 SP Reagent v1.5 Kit (300 Cycles); PN 20028400</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000459</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq 6000 S4 Reagent v1.5 Kit (200 Cycles); PN 20028313</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000259</t>
-  </si>
-  <si>
-    <t>Illumina; NextSeq 500/550 Hi Output Kit 75 Cycles v2.5; PN 20024906</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000381</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq 6000 S4 Reagent Kit v1.5 (300 cycles); PN 20028312</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000319</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq X Series 10B Reagent Kit (100 Cycle); PN 20085596</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000285</t>
-  </si>
-  <si>
-    <t>Illumina; NovaSeq 6000 S2 Reagent v1.5 Kit (100 Cycles); PN 20028316</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000258</t>
+    <t>Element Biosciences; AVITI 2x150 Sequencing Kit Cloudbreak FS High Output (334 Cycles); PN 860-00013</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000513</t>
   </si>
   <si>
     <t>sequencing_read_format</t>
@@ -2489,37 +2564,73 @@
     <t>preparation_instrument_vendor</t>
   </si>
   <si>
+    <t>HTX Technologies</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023734</t>
+  </si>
+  <si>
+    <t>SunChrom</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023908</t>
+  </si>
+  <si>
     <t>Roche Diagnostics</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_025096</t>
   </si>
   <si>
-    <t>HTX Technologies</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023734</t>
-  </si>
-  <si>
-    <t>SunChrom</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023908</t>
-  </si>
-  <si>
     <t>preparation_instrument_model</t>
   </si>
   <si>
+    <t>Chromium Controller</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_019326</t>
+  </si>
+  <si>
     <t>Sublimator</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_023729</t>
   </si>
   <si>
-    <t>Chromium Controller</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_019326</t>
+    <t>M3+ Sprayer</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023731</t>
+  </si>
+  <si>
+    <t>TM-Sprayer</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023732</t>
+  </si>
+  <si>
+    <t>M5 Sprayer</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023733</t>
+  </si>
+  <si>
+    <t>SunCollect Sprayer</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023907</t>
+  </si>
+  <si>
+    <t>AutoStainer XL</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023957</t>
+  </si>
+  <si>
+    <t>Chromium iX</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024536</t>
   </si>
   <si>
     <t>Chromium X</t>
@@ -2528,28 +2639,16 @@
     <t>https://identifiers.org/RRID:SCR_024537</t>
   </si>
   <si>
-    <t>AutoStainer XL</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023957</t>
-  </si>
-  <si>
     <t>Visium CytAssist</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_024570</t>
   </si>
   <si>
-    <t>SunCollect Sprayer</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023907</t>
-  </si>
-  <si>
-    <t>M3+ Sprayer</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023731</t>
+    <t>ST5020 Multistainer</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_025021</t>
   </si>
   <si>
     <t>Discovery Ultra</t>
@@ -2558,127 +2657,103 @@
     <t>https://identifiers.org/RRID:SCR_025097</t>
   </si>
   <si>
-    <t>ST5020 Multistainer</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_025021</t>
-  </si>
-  <si>
-    <t>Chromium iX</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024536</t>
-  </si>
-  <si>
     <t>Chromium Connect</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_025146</t>
   </si>
   <si>
-    <t>M5 Sprayer</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023733</t>
-  </si>
-  <si>
-    <t>TM-Sprayer</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023732</t>
-  </si>
-  <si>
     <t>preparation_instrument_kit</t>
   </si>
   <si>
+    <t>10x Genomics; Chromium Next GEM Chip J Single Cell Kit, 48 rxns; PN 1000234</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000262</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Next GEM Chip J Single Cell Kit, 16 rxns; PN 1000230</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000263</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium FFPE Reagent Kit v2-Small, PN 1000436</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000324</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Chip Q Single Cell Kit, 16 rxns; PN 1000422</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000325</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 48 rxns; PN 1000286</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000367</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 16 rxns; PN 1000287</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000368</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Chip K Automated Single Cell Kit, 48 rxns; PN 1000289</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000373</t>
   </si>
   <si>
+    <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 48 rxns; PN 1000120</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000378</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 16 rxns; PN 1000127</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000379</t>
+  </si>
+  <si>
     <t>10x Genomics; Chromium Single Cell B Chip Kit, 16 rxns; PN 1000074</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000462</t>
   </si>
   <si>
+    <t>10x Genomics; Chromium Chip E Single Cell ATAC Kit, 48 rxns; PN 1000155</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000470</t>
+  </si>
+  <si>
+    <t>10x Genomics; Visium HD, Human Transcriptome, 6.5 mm, 4 runs; PN 1000675</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000493</t>
+  </si>
+  <si>
     <t>10x Genomics; Visium HD, Mouse Transcriptome, 6.5 mm, 4 runs; PN 1000676</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000494</t>
   </si>
   <si>
-    <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 48 rxns; PN 1000286</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000367</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Chip E Single Cell ATAC Kit, 48 rxns; PN 1000155</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000470</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 48 rxns; PN 1000120</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000378</t>
-  </si>
-  <si>
-    <t>10x Genomics; Visium HD, Human Transcriptome, 6.5 mm, 4 runs; PN 1000675</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000493</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 16 rxns; PN 1000287</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000368</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Next GEM Chip J Single Cell Kit, 16 rxns; PN 1000230</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000263</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 16 rxns; PN 1000127</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000379</t>
-  </si>
-  <si>
     <t>10x Genomics; Visium HD, Human Transcriptome, 11 mm, 4 runs; PN 1001037</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000495</t>
   </si>
   <si>
-    <t>10x Genomics; Chromium GEM-X Single Cell 3' Kit v4, 16 rxns; PN 1000691</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000400</t>
-  </si>
-  <si>
-    <t>10X Genomics; Visium FFPE Reagent Kit v2-Small, PN 1000436</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000324</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Chip Q Single Cell Kit, 16 rxns; PN 1000422</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000325</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Next GEM Chip J Single Cell Kit, 48 rxns; PN 1000234</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000262</t>
+    <t>10x Genomics; Visium HD, Mouse Transcriptome, 11 mm, 4 runs; PN 1001038</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000496</t>
   </si>
   <si>
     <t>10x Genomics; GEM-X Flex Gene Expression Chip Kit, 4 chips; PN 1000791</t>
@@ -2687,12 +2762,6 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000498</t>
   </si>
   <si>
-    <t>10x Genomics; Visium HD, Mouse Transcriptome, 11 mm, 4 runs; PN 1001038</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000496</t>
-  </si>
-  <si>
     <t>probe_hybridization_time_value</t>
   </si>
   <si>
@@ -2702,22 +2771,100 @@
     <t>oligo_probe_panel</t>
   </si>
   <si>
+    <t>10x Genomics; Visium Human Transcriptome Probe Kit v2 - Small; PN 1000466</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000274</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Fixed RNA Kit, Human Transcriptome, 4 rxns x 1 BC; PN 1000474</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000306</t>
+  </si>
+  <si>
+    <t>10x Genomics; Visium Human Transcriptome Probe Kit-Small; PN 1000363</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000326</t>
+  </si>
+  <si>
+    <t>10x Genomics; Visium Mouse Transcriptome Probe Kit - Small; PN 1000365</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000362</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; GeoMx Human Whole Transcriptome Atlas, 4 slides; PN GMX-RNA-NGS-HuWTA-4</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000363</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; GeoMx Mouse Whole Transcriptome Atlas, 4 slides; PN GMX-RNA-NGS-MsWTA-4</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000364</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Human Transcriptome Probe Kit, 64 rxns; PN 1000456</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000376</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Human Transcriptome Probe Kit, 16 rxns; PN 1000420</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000382</t>
+  </si>
+  <si>
+    <t>10x Genomics; Visium Human Transcriptome Probe Kit-Large; PN 1000364</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000383</t>
+  </si>
+  <si>
     <t>10x Genomics; Chromium Next GEM Single Cell Fixed RNA Mouse Transcriptome Probe Kit, 64 rxns; PN 1000492</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000393</t>
   </si>
   <si>
+    <t>10x Genomics; Xenium Human Multi-Tissue and Cancer Panel v1; PN 1000626</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000395</t>
+  </si>
+  <si>
     <t>10x Genomics; Xenium Prime 5K Human Pan Tissue &amp; Pathways Panel; PN 1000724</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000426</t>
   </si>
   <si>
-    <t>10x Genomics; Visium Human Transcriptome Probe Kit-Large; PN 1000364</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000383</t>
+    <t>NanoString Technologies; CosMx Human Universal Cell Characterization Panel (RNA, 1000 Plex); PN CMX-H-USCP-1KP-R</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000430</t>
+  </si>
+  <si>
+    <t>10x Genomics; Visium Mouse Transcriptome Probe Kit v2.0 - Small; PN 1000667</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000431</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; CosMx Human Immuno-Oncology Panel (Protein, 64 Plex); PN CMX-H-IOP-64P-P</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000436</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; CosMx Mouse Neuroscience Panel (Protein, 64 Plex); PN CMX-M-Neuro-64P-P</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000437</t>
   </si>
   <si>
     <t>10x Genomics; Xenium Mouse Multi-Tissue Atlassing Panel; PN 1000627</t>
@@ -2726,160 +2873,88 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000442</t>
   </si>
   <si>
+    <t>10x Genomics; Xenium Human Lung Gene Expression Panel; PN 1000601</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000443</t>
+  </si>
+  <si>
+    <t>10x Genomics; Xenium Custom Gene Expression Panel (51-100 genes); PN 1000561</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000444</t>
+  </si>
+  <si>
+    <t>10x Genomics; Xenium Custom Gene Expression Panel (up to 50 genes); PN 1000464</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000445</t>
+  </si>
+  <si>
+    <t>10x Genomics; Xenium Human Colon Gene Expression Panel; PN 1000642</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000446</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; CosMx Mouse Neuroscience Panel (RNA, 1000 Plex); PN CMX-M-NEUP-R</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000452</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; CosMx Hs WTX RNA Panel Kit, 2 slides: PN 121500047</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000453</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; CosMx Hs Univ Cell (RNA, 1000 Plex); PN 121500002</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000454</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; CosMx Human 6K Discovery Panel (RNA, 6175 Plex); PN 121500041</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000455</t>
+  </si>
+  <si>
+    <t>NanoString Technologies; CosMx Mouse Universal Cell Characterization Panel (RNA, 1000 Plex); PN CMX-M-USCP-1KP-R</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000457</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Fixed RNA Kit, Human Transcriptome 16 rxns x 16 BC; PN 1000547</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000477</t>
+  </si>
+  <si>
     <t>10x Genomics; GEM-X Flex Human Transcriptome Probe Kit, 16 samples; PN 1000785</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000481</t>
   </si>
   <si>
-    <t>10x Genomics; Visium Human Transcriptome Probe Kit-Small; PN 1000363</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000326</t>
-  </si>
-  <si>
-    <t>10x Genomics; Visium Mouse Transcriptome Probe Kit v2.0 - Small; PN 1000667</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000431</t>
-  </si>
-  <si>
     <t>NanoString Technologies; GeoMx Human IO Proteome Atlas, 4 slides; PN 121300160</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000488</t>
   </si>
   <si>
-    <t>10x Genomics; Visium Human Transcriptome Probe Kit v2 - Small; PN 1000466</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000274</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; CosMx Human 6K Discovery Panel (RNA, 6175 Plex); PN 121500041</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000455</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; CosMx Mouse Universal Cell Characterization Panel (RNA, 1000 Plex); PN CMX-M-USCP-1KP-R</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000457</t>
-  </si>
-  <si>
-    <t>10x Genomics; Xenium Custom Gene Expression Panel (51-100 genes); PN 1000561</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000444</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Human Transcriptome Probe Kit, 64 rxns; PN 1000456</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000376</t>
-  </si>
-  <si>
-    <t>10x Genomics; Xenium Human Colon Gene Expression Panel; PN 1000642</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000446</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; CosMx Human Immuno-Oncology Panel (Protein, 64 Plex); PN CMX-H-IOP-64P-P</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000436</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Fixed RNA Kit, Human Transcriptome 16 rxns x 16 BC; PN 1000547</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000477</t>
-  </si>
-  <si>
-    <t>10x Genomics; Visium Mouse Transcriptome Probe Kit - Small; PN 1000365</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000362</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; CosMx Hs WTX RNA Panel Kit, 2 slides: PN 121500047</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000453</t>
-  </si>
-  <si>
-    <t>10x Genomics; Xenium Human Lung Gene Expression Panel; PN 1000601</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000443</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; CosMx Mouse Neuroscience Panel (Protein, 64 Plex); PN CMX-M-Neuro-64P-P</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000437</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; GeoMx Mouse Whole Transcriptome Atlas, 4 slides; PN GMX-RNA-NGS-MsWTA-4</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000364</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; CosMx Mouse Neuroscience Panel (RNA, 1000 Plex); PN CMX-M-NEUP-R</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000452</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; GeoMx Human Whole Transcriptome Atlas, 4 slides; PN GMX-RNA-NGS-HuWTA-4</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000363</t>
-  </si>
-  <si>
-    <t>10x Genomics; Xenium Human Multi-Tissue and Cancer Panel v1; PN 1000626</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000395</t>
-  </si>
-  <si>
-    <t>10x Genomics; Xenium Custom Gene Expression Panel (up to 50 genes); PN 1000464</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000445</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Fixed RNA Kit, Human Transcriptome, 4 rxns x 1 BC; PN 1000474</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000306</t>
-  </si>
-  <si>
     <t>10x Genomics; Xenium Human Skin Gene Expression Panel; PN 1000643</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000491</t>
   </si>
   <si>
-    <t>NanoString Technologies; CosMx Human Universal Cell Characterization Panel (RNA, 1000 Plex); PN CMX-H-USCP-1KP-R</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000430</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Human Transcriptome Probe Kit, 16 rxns; PN 1000420</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000382</t>
-  </si>
-  <si>
-    <t>NanoString Technologies; CosMx Hs Univ Cell (RNA, 1000 Plex); PN 121500002</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000454</t>
+    <t>10x Genomics; Xenium Prime 5K Mouse Pan Tissues &amp; Pathways Panel, 2 rxns; PN 1000725</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000506</t>
   </si>
   <si>
     <t>is_custom_probes_used</t>
@@ -2903,7 +2978,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2026-08-26T14:13:11-07:00</t>
+    <t>2026-10-21T13:32:03-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -3105,162 +3180,162 @@
         <v>4</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>612</v>
+        <v>635</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>613</v>
+        <v>636</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>614</v>
+        <v>637</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>615</v>
+        <v>638</v>
       </c>
       <c r="AQ1" t="s" s="1">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="AR1" t="s" s="1">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="AS1" t="s" s="1">
-        <v>676</v>
+        <v>701</v>
       </c>
       <c r="AT1" t="s" s="1">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="AU1" t="s" s="1">
-        <v>684</v>
+        <v>709</v>
       </c>
       <c r="AV1" t="s" s="1">
-        <v>711</v>
+        <v>736</v>
       </c>
       <c r="AW1" t="s" s="1">
-        <v>746</v>
+        <v>769</v>
       </c>
       <c r="AX1" t="s" s="1">
-        <v>747</v>
+        <v>770</v>
       </c>
       <c r="AY1" t="s" s="1">
-        <v>748</v>
+        <v>771</v>
       </c>
       <c r="AZ1" t="s" s="1">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="BA1" t="s" s="1">
-        <v>810</v>
+        <v>835</v>
       </c>
     </row>
     <row r="2">
       <c r="E2" t="s" s="6">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="BA2" t="s" s="54">
-        <v>811</v>
+        <v>836</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="41">
     <dataValidation type="list" sqref="E2:E1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'dataset_type'!$A$1:$A$59</formula1>
+      <formula1>'dataset_type'!$A$1:$A$60</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F2:F1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'analyte_class'!$A$1:$A$18</formula1>
@@ -3269,10 +3344,10 @@
       <formula1>'is_targeted'!$A$1:$A$2</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="H2:H1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'acquisition_instrument_vendor'!$A$1:$A$33</formula1>
+      <formula1>'acquisition_instrument_vendor'!$A$1:$A$35</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I2:I1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'acquisition_instrument_model'!$A$1:$A$89</formula1>
+      <formula1>'acquisition_instrument_model'!$A$1:$A$91</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="J2:J1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
       <formula1>0</formula1>
@@ -3357,10 +3432,10 @@
       <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation type="list" sqref="AK2:AK1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'library_preparation_kit'!$A$1:$A$40</formula1>
+      <formula1>'library_preparation_kit'!$A$1:$A$42</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AL2:AL1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'sample_indexing_kit'!$A$1:$A$20</formula1>
+      <formula1>'sample_indexing_kit'!$A$1:$A$25</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AN2:AN1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'is_technical_replicate'!$A$1:$A$2</formula1>
@@ -3370,7 +3445,7 @@
       <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation type="list" sqref="AP2:AP1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'sequencing_reagent_kit'!$A$1:$A$30</formula1>
+      <formula1>'sequencing_reagent_kit'!$A$1:$A$31</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AT2:AT1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'preparation_instrument_vendor'!$A$1:$A$11</formula1>
@@ -3389,7 +3464,7 @@
       <formula1>'probe_hybridization_time_unit'!$A$1:$A$2</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AY2:AY1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'oligo_probe_panel'!$A$1:$A$31</formula1>
+      <formula1>'oligo_probe_panel'!$A$1:$A$32</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AZ2:AZ1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'is_custom_probes_used'!$A$1:$A$2</formula1>
@@ -3408,26 +3483,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>239</v>
+        <v>445</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>240</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>436</v>
+        <v>238</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>437</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3442,42 +3517,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3492,22 +3567,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3522,26 +3597,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>239</v>
+        <v>445</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>240</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>436</v>
+        <v>238</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>437</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3556,32 +3631,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>450</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3596,42 +3671,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>463</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -3646,18 +3721,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>468</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>470</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -3672,18 +3747,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>470</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -3698,18 +3773,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>470</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -3724,26 +3799,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>482</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>484</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>486</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -3753,7 +3828,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4226,6 +4301,14 @@
       </c>
       <c r="B59" t="s" s="0">
         <v>122</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -4240,18 +4323,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>489</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>491</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -4261,327 +4344,343 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>496</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>500</v>
+        <v>509</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>502</v>
+        <v>511</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>504</v>
+        <v>513</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>506</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>508</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>510</v>
+        <v>519</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>512</v>
+        <v>521</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>514</v>
+        <v>523</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>516</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>518</v>
+        <v>527</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>520</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>524</v>
+        <v>533</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>526</v>
+        <v>535</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>528</v>
+        <v>537</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>530</v>
+        <v>539</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>532</v>
+        <v>541</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>534</v>
+        <v>543</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>536</v>
+        <v>545</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>538</v>
+        <v>547</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>540</v>
+        <v>549</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>542</v>
+        <v>551</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>544</v>
+        <v>553</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>546</v>
+        <v>555</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>548</v>
+        <v>557</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>550</v>
+        <v>559</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>552</v>
+        <v>561</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>554</v>
+        <v>563</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>556</v>
+        <v>565</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>558</v>
+        <v>567</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>560</v>
+        <v>569</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>562</v>
+        <v>571</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>564</v>
+        <v>573</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>566</v>
+        <v>575</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>568</v>
+        <v>577</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>570</v>
+        <v>579</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>572</v>
+        <v>581</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>574</v>
+        <v>583</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>584</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>586</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -4591,167 +4690,207 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>576</v>
+        <v>238</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>577</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>578</v>
+        <v>504</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>579</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>239</v>
+        <v>589</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>240</v>
+        <v>590</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>581</v>
+        <v>592</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>583</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>585</v>
+        <v>596</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>587</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>589</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>591</v>
+        <v>602</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>593</v>
+        <v>604</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>553</v>
+        <v>605</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>554</v>
+        <v>606</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>594</v>
+        <v>607</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>595</v>
+        <v>608</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>596</v>
+        <v>609</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>597</v>
+        <v>610</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>599</v>
+        <v>612</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>601</v>
+        <v>614</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>603</v>
+        <v>616</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>605</v>
+        <v>618</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>606</v>
+        <v>619</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>607</v>
+        <v>620</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>609</v>
+        <v>622</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>610</v>
+        <v>623</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>611</v>
+        <v>624</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>625</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>627</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>629</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>631</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>633</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>634</v>
       </c>
     </row>
   </sheetData>
@@ -4766,12 +4905,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -4781,247 +4920,255 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>616</v>
+        <v>504</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>617</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>619</v>
+        <v>640</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>621</v>
+        <v>642</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>624</v>
+        <v>645</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>625</v>
+        <v>646</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>627</v>
+        <v>648</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>629</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>630</v>
+        <v>651</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>631</v>
+        <v>652</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>632</v>
+        <v>653</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>633</v>
+        <v>654</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>634</v>
+        <v>655</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>635</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>637</v>
+        <v>658</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>638</v>
+        <v>659</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>639</v>
+        <v>660</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>640</v>
+        <v>661</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>641</v>
+        <v>662</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>642</v>
+        <v>663</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>643</v>
+        <v>664</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>645</v>
+        <v>666</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>646</v>
+        <v>667</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>647</v>
+        <v>668</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>649</v>
+        <v>670</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>651</v>
+        <v>672</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>553</v>
+        <v>673</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>554</v>
+        <v>674</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>652</v>
+        <v>675</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>653</v>
+        <v>676</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>654</v>
+        <v>677</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>655</v>
+        <v>678</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>656</v>
+        <v>679</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>657</v>
+        <v>680</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>658</v>
+        <v>681</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>659</v>
+        <v>682</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>660</v>
+        <v>683</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>661</v>
+        <v>684</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>662</v>
+        <v>685</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>663</v>
+        <v>686</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>664</v>
+        <v>687</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>665</v>
+        <v>688</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>666</v>
+        <v>689</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>667</v>
+        <v>690</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>668</v>
+        <v>691</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>669</v>
+        <v>692</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>670</v>
+        <v>693</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>671</v>
+        <v>694</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>672</v>
+        <v>695</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>673</v>
+        <v>696</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>697</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>698</v>
       </c>
     </row>
   </sheetData>
@@ -5036,90 +5183,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>197</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>217</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>239</v>
+        <v>169</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>240</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>678</v>
+        <v>183</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>679</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>680</v>
+        <v>187</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>681</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>223</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>226</v>
+        <v>703</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>227</v>
+        <v>704</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>180</v>
+        <v>705</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>181</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>682</v>
+        <v>707</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>683</v>
+        <v>708</v>
       </c>
     </row>
   </sheetData>
@@ -5134,154 +5281,154 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>321</v>
+        <v>238</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>322</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>239</v>
+        <v>504</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>240</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>686</v>
+        <v>711</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>243</v>
+        <v>712</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>244</v>
+        <v>713</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>687</v>
+        <v>714</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>688</v>
+        <v>715</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>553</v>
+        <v>716</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>554</v>
+        <v>717</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>301</v>
+        <v>718</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>302</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>392</v>
+        <v>310</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>393</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>689</v>
+        <v>312</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>690</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>691</v>
+        <v>314</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>692</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>693</v>
+        <v>720</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>694</v>
+        <v>721</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>695</v>
+        <v>722</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>696</v>
+        <v>723</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>697</v>
+        <v>724</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>698</v>
+        <v>725</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>700</v>
+        <v>727</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>702</v>
+        <v>729</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>703</v>
+        <v>730</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>704</v>
+        <v>731</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>705</v>
+        <v>346</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>706</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>707</v>
+        <v>732</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>708</v>
+        <v>733</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>709</v>
+        <v>734</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>710</v>
+        <v>735</v>
       </c>
     </row>
   </sheetData>
@@ -5296,162 +5443,162 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>712</v>
+        <v>504</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>713</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>714</v>
+        <v>506</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>715</v>
+        <v>507</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>549</v>
+        <v>508</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>550</v>
+        <v>509</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>716</v>
+        <v>737</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>717</v>
+        <v>738</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>719</v>
+        <v>740</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>721</v>
+        <v>742</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>723</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>553</v>
+        <v>745</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>554</v>
+        <v>746</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>725</v>
+        <v>748</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>726</v>
+        <v>749</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>727</v>
+        <v>750</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>728</v>
+        <v>751</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>729</v>
+        <v>752</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>730</v>
+        <v>753</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>731</v>
+        <v>754</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>732</v>
+        <v>755</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>733</v>
+        <v>756</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>734</v>
+        <v>757</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>735</v>
+        <v>758</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>736</v>
+        <v>759</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>737</v>
+        <v>760</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>738</v>
+        <v>761</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>739</v>
+        <v>762</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>740</v>
+        <v>763</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>742</v>
+        <v>765</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>743</v>
+        <v>766</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>744</v>
+        <v>767</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>745</v>
+        <v>768</v>
       </c>
     </row>
   </sheetData>
@@ -5466,18 +5613,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -5487,255 +5634,263 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>749</v>
+        <v>504</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>750</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>751</v>
+        <v>772</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>752</v>
+        <v>773</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>754</v>
+        <v>775</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>755</v>
+        <v>776</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>756</v>
+        <v>777</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>757</v>
+        <v>778</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>758</v>
+        <v>779</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>759</v>
+        <v>780</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>760</v>
+        <v>781</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>761</v>
+        <v>782</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>762</v>
+        <v>783</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>763</v>
+        <v>784</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>764</v>
+        <v>785</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>765</v>
+        <v>786</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>766</v>
+        <v>787</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>767</v>
+        <v>788</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>768</v>
+        <v>789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>769</v>
+        <v>790</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>770</v>
+        <v>791</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>771</v>
+        <v>792</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>772</v>
+        <v>793</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>773</v>
+        <v>794</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>774</v>
+        <v>795</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>775</v>
+        <v>796</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>776</v>
+        <v>797</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>777</v>
+        <v>798</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>778</v>
+        <v>799</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>779</v>
+        <v>800</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>780</v>
+        <v>801</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>782</v>
+        <v>803</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>783</v>
+        <v>804</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>784</v>
+        <v>805</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>785</v>
+        <v>806</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>786</v>
+        <v>807</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>788</v>
+        <v>809</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>790</v>
+        <v>811</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>791</v>
+        <v>812</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>792</v>
+        <v>813</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>553</v>
+        <v>814</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>554</v>
+        <v>815</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>793</v>
+        <v>816</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>794</v>
+        <v>817</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>795</v>
+        <v>818</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>796</v>
+        <v>819</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>797</v>
+        <v>820</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>798</v>
+        <v>821</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>799</v>
+        <v>822</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>800</v>
+        <v>823</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>801</v>
+        <v>824</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>802</v>
+        <v>825</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>803</v>
+        <v>826</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>804</v>
+        <v>827</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>805</v>
+        <v>828</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>806</v>
+        <v>829</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>807</v>
+        <v>830</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>808</v>
+        <v>831</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>832</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>833</v>
       </c>
     </row>
   </sheetData>
@@ -5750,146 +5905,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -5904,12 +6059,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -5930,30 +6085,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>812</v>
+        <v>837</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>813</v>
+        <v>838</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>815</v>
+        <v>840</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>817</v>
+        <v>842</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>816</v>
+        <v>841</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>818</v>
+        <v>843</v>
       </c>
     </row>
   </sheetData>
@@ -5968,12 +6123,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -5983,271 +6138,287 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>229</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -6257,719 +6428,735 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>231</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>232</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>196</v>
+        <v>378</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>197</v>
+        <v>379</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>384</v>
+        <v>5</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B87" t="s" s="0">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B88" t="s" s="0">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B89" t="s" s="0">
-        <v>405</v>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>411</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>413</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -6984,42 +7171,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>415</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -7034,26 +7221,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>411</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>413</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>415</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -7068,57 +7255,57 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>426</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
